--- a/DataIA/1.Transformaciones Variables.xlsx
+++ b/DataIA/1.Transformaciones Variables.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA9F362-1982-4403-B6AD-5EB2C11A183F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D2D3B3-9FB8-4648-907F-604BCD291DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
   <si>
     <t>sexo</t>
   </si>
@@ -239,15 +239,6 @@
     <t>pais_España</t>
   </si>
   <si>
-    <t>nSatis_meGusta</t>
-  </si>
-  <si>
-    <t>nSatis_neutral</t>
-  </si>
-  <si>
-    <t>nSatis_noMeGusta</t>
-  </si>
-  <si>
     <t>mean pais brasil</t>
   </si>
   <si>
@@ -276,12 +267,6 @@
   </si>
   <si>
     <t>std meGusta</t>
-  </si>
-  <si>
-    <t>mean Neutral</t>
-  </si>
-  <si>
-    <t>std Neutral</t>
   </si>
   <si>
     <t>mean sexo_M</t>
@@ -488,7 +473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -522,6 +507,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -534,15 +527,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1174,12 +1158,12 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1323,12 +1307,12 @@
       <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1510,7 +1494,8 @@
     <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" customWidth="1"/>
     <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.140625" customWidth="1"/>
@@ -1626,59 +1611,59 @@
       <c r="G8" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1744,10 +1729,10 @@
         <v>30</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1870,12 +1855,12 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
       <c r="E33" s="5"/>
       <c r="L33" t="s">
         <v>59</v>
@@ -1908,13 +1893,7 @@
         <v>67</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="L34" t="s">
         <v>60</v>
@@ -1947,13 +1926,8 @@
       <c r="G35" s="1">
         <v>0</v>
       </c>
-      <c r="H35" s="1">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
+      <c r="H35" s="2">
+        <f>(E24-$M$34)/($M$33-$M$34)</f>
         <v>0</v>
       </c>
     </row>
@@ -1965,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="2">
-        <f>(C25-$M$40)/($M$39-$M$40)</f>
+        <f t="shared" ref="C35:C40" si="0">(C25-$M$40)/($M$39-$M$40)</f>
         <v>0.30357142857142855</v>
       </c>
       <c r="D36" s="2">
@@ -1980,13 +1954,8 @@
       <c r="G36" s="1">
         <v>1</v>
       </c>
-      <c r="H36" s="1">
-        <v>0</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0</v>
-      </c>
-      <c r="J36" s="1">
+      <c r="H36" s="2">
+        <f>(E25-$M$34)/($M$33-$M$34)</f>
         <v>1</v>
       </c>
       <c r="L36" t="s">
@@ -2005,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="2">
-        <f>(C26-$M$40)/($M$39-$M$40)</f>
+        <f t="shared" si="0"/>
         <v>0.21428571428571427</v>
       </c>
       <c r="D37" s="2">
@@ -2020,14 +1989,9 @@
       <c r="G37" s="1">
         <v>0</v>
       </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
-      <c r="I37" s="1">
-        <v>1</v>
-      </c>
-      <c r="J37" s="1">
-        <v>0</v>
+      <c r="H37" s="2">
+        <f>(E26-$M$34)/($M$33-$M$34)</f>
+        <v>0.5</v>
       </c>
       <c r="L37" t="s">
         <v>62</v>
@@ -2045,7 +2009,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="2">
-        <f>(C27-$M$40)/($M$39-$M$40)</f>
+        <f t="shared" si="0"/>
         <v>5.3571428571428568E-2</v>
       </c>
       <c r="D38" s="2">
@@ -2060,13 +2024,8 @@
       <c r="G38" s="1">
         <v>0</v>
       </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1">
+      <c r="H38" s="2">
+        <f t="shared" ref="H36:H40" si="1">(E27-$M$34)/($M$33-$M$34)</f>
         <v>1</v>
       </c>
     </row>
@@ -2078,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="C39" s="2">
-        <f>(C28-$M$40)/($M$39-$M$40)</f>
+        <f t="shared" si="0"/>
         <v>0.4107142857142857</v>
       </c>
       <c r="D39" s="2">
@@ -2093,13 +2052,8 @@
       <c r="G39" s="1">
         <v>1</v>
       </c>
-      <c r="H39" s="1">
-        <v>1</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1">
+      <c r="H39" s="2">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L39" t="s">
@@ -2118,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="2">
-        <f>(C29-$M$40)/($M$39-$M$40)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D40" s="2">
@@ -2133,13 +2087,8 @@
       <c r="G40" s="1">
         <v>0</v>
       </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1">
+      <c r="H40" s="2">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L40" t="s">
@@ -2151,12 +2100,12 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
@@ -2181,13 +2130,7 @@
         <v>67</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="M44" t="s">
         <v>20</v>
@@ -2197,11 +2140,11 @@
         <v>27.5</v>
       </c>
       <c r="P44" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q44">
-        <f>AVERAGE(H35:H40)</f>
-        <v>0.33333333333333331</v>
+        <f>AVERAGE(E24:E29)</f>
+        <v>1.1666666666666667</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -2218,7 +2161,7 @@
         <v>2.0270270270270272</v>
       </c>
       <c r="E45" s="2">
-        <f>(D35-$N$47)/$N$48</f>
+        <f t="shared" ref="E45:E50" si="2">(D35-$N$47)/$N$48</f>
         <v>2.2360679774997898</v>
       </c>
       <c r="F45" s="2">
@@ -2234,16 +2177,8 @@
         <v>-0.70710678118654746</v>
       </c>
       <c r="I45" s="2">
-        <f>(H35-$Q$44)/$Q$45</f>
-        <v>1.4142135623730951</v>
-      </c>
-      <c r="J45" s="2">
-        <f>(I35-$Q$47)/$Q$48</f>
-        <v>-0.44721359549995793</v>
-      </c>
-      <c r="K45" s="2">
-        <f>(J35-$Q$50)/$Q$51</f>
-        <v>-1</v>
+        <f>(E24-$Q$44)/$Q$45</f>
+        <v>-1.2998673672393632</v>
       </c>
       <c r="M45" t="s">
         <v>24</v>
@@ -2253,379 +2188,295 @@
         <v>18.5</v>
       </c>
       <c r="P45" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="Q45">
-        <f>_xlfn.STDEV.P(H35:H40)</f>
-        <v>0.47140452079103168</v>
+        <f>_xlfn.STDEV.P(E24:E29)</f>
+        <v>0.89752746785575066</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
-        <f t="shared" ref="B46:B50" si="0">(A36-$Q$53)/$Q$54</f>
+        <f t="shared" ref="B46:B50" si="3">(A36-$Q$53)/$Q$54</f>
         <v>-1</v>
       </c>
       <c r="C46" s="1">
-        <f t="shared" ref="C46:C50" si="1">(B36-$Q$56)/$Q$57</f>
+        <f t="shared" ref="C46:C50" si="4">(B36-$Q$56)/$Q$57</f>
         <v>1</v>
       </c>
       <c r="D46" s="2">
-        <f>(C25-$N$44)/$N$45</f>
+        <f t="shared" ref="D45:D50" si="5">(C25-$N$44)/$N$45</f>
         <v>-8.1081081081081086E-2</v>
       </c>
       <c r="E46" s="2">
-        <f>(D36-$N$47)/$N$48</f>
+        <f t="shared" si="2"/>
         <v>-0.44721359549995793</v>
       </c>
       <c r="F46" s="2">
-        <f t="shared" ref="F46:F50" si="2">(E36-$N$50)/$N$51</f>
+        <f t="shared" ref="F46:F50" si="6">(E36-$N$50)/$N$51</f>
         <v>-0.44721359549995793</v>
       </c>
       <c r="G46" s="2">
-        <f t="shared" ref="G46:G50" si="3">(F36-$N$53)/$N$54</f>
+        <f t="shared" ref="G46:G50" si="7">(F36-$N$53)/$N$54</f>
         <v>-0.70710678118654746</v>
       </c>
       <c r="H46" s="2">
-        <f t="shared" ref="H46:H50" si="4">(G36-$N$56)/$N$57</f>
+        <f t="shared" ref="H46:H50" si="8">(G36-$N$56)/$N$57</f>
         <v>1.4142135623730951</v>
       </c>
       <c r="I46" s="2">
-        <f t="shared" ref="I46:I50" si="5">(H36-$Q$44)/$Q$45</f>
-        <v>-0.70710678118654746</v>
-      </c>
-      <c r="J46" s="2">
-        <f t="shared" ref="J46:J50" si="6">(I36-$Q$47)/$Q$48</f>
-        <v>-0.44721359549995793</v>
-      </c>
-      <c r="K46" s="2">
-        <f t="shared" ref="K46:K50" si="7">(J36-$Q$50)/$Q$51</f>
-        <v>1</v>
+        <f>(E25-$Q$44)/$Q$45</f>
+        <v>0.92847669088525919</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="C47" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-1</v>
       </c>
       <c r="D47" s="2">
-        <f>(C26-$N$44)/$N$45</f>
+        <f t="shared" si="5"/>
         <v>-0.35135135135135137</v>
       </c>
       <c r="E47" s="2">
-        <f>(D37-$N$47)/$N$48</f>
+        <f t="shared" si="2"/>
         <v>-0.44721359549995793</v>
       </c>
       <c r="F47" s="2">
-        <f t="shared" si="2"/>
-        <v>2.2360679774997898</v>
-      </c>
-      <c r="G47" s="2">
-        <f t="shared" si="3"/>
-        <v>-0.70710678118654746</v>
-      </c>
-      <c r="H47" s="2">
-        <f t="shared" si="4"/>
-        <v>-0.70710678118654746</v>
-      </c>
-      <c r="I47" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.70710678118654746</v>
-      </c>
-      <c r="J47" s="2">
         <f t="shared" si="6"/>
         <v>2.2360679774997898</v>
       </c>
-      <c r="K47" s="2">
+      <c r="G47" s="2">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="H47" s="2">
+        <f t="shared" si="8"/>
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="I47" s="2">
+        <f>(E26-$Q$44)/$Q$45</f>
+        <v>-0.18569533817705194</v>
       </c>
       <c r="M47" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N47">
         <f>AVERAGE(D35:D40)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="P47" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q47">
-        <f>AVERAGE(I35:I40)</f>
-        <v>0.16666666666666666</v>
-      </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B48" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="C48" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D48" s="2">
-        <f>(C27-$N$44)/$N$45</f>
+        <f t="shared" si="5"/>
         <v>-0.83783783783783783</v>
       </c>
       <c r="E48" s="2">
-        <f>(D38-$N$47)/$N$48</f>
-        <v>-0.44721359549995793</v>
-      </c>
-      <c r="F48" s="2">
         <f t="shared" si="2"/>
         <v>-0.44721359549995793</v>
       </c>
-      <c r="G48" s="2">
-        <f t="shared" si="3"/>
-        <v>1.4142135623730951</v>
-      </c>
-      <c r="H48" s="2">
-        <f t="shared" si="4"/>
-        <v>-0.70710678118654746</v>
-      </c>
-      <c r="I48" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.70710678118654746</v>
-      </c>
-      <c r="J48" s="2">
+      <c r="F48" s="2">
         <f t="shared" si="6"/>
         <v>-0.44721359549995793</v>
       </c>
-      <c r="K48" s="2">
+      <c r="G48" s="2">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="H48" s="2">
+        <f t="shared" si="8"/>
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="I48" s="2">
+        <f>(E27-$Q$44)/$Q$45</f>
+        <v>0.92847669088525919</v>
       </c>
       <c r="M48" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N48">
         <f>_xlfn.STDEV.P(D35:D40)</f>
         <v>0.37267799624996495</v>
       </c>
-      <c r="P48" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q48">
-        <f>_xlfn.STDEV.P(I35:I40)</f>
-        <v>0.37267799624996495</v>
-      </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B49" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="C49" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>-1</v>
       </c>
       <c r="D49" s="2">
-        <f>(C28-$N$44)/$N$45</f>
+        <f t="shared" si="5"/>
         <v>0.24324324324324326</v>
       </c>
       <c r="E49" s="2">
-        <f>(D39-$N$47)/$N$48</f>
-        <v>-0.44721359549995793</v>
-      </c>
-      <c r="F49" s="2">
         <f t="shared" si="2"/>
         <v>-0.44721359549995793</v>
       </c>
-      <c r="G49" s="2">
-        <f t="shared" si="3"/>
-        <v>-0.70710678118654746</v>
-      </c>
-      <c r="H49" s="2">
-        <f t="shared" si="4"/>
-        <v>1.4142135623730951</v>
-      </c>
-      <c r="I49" s="2">
-        <f t="shared" si="5"/>
-        <v>1.4142135623730951</v>
-      </c>
-      <c r="J49" s="2">
+      <c r="F49" s="2">
         <f t="shared" si="6"/>
         <v>-0.44721359549995793</v>
       </c>
-      <c r="K49" s="2">
+      <c r="G49" s="2">
         <f t="shared" si="7"/>
-        <v>-1</v>
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="H49" s="2">
+        <f t="shared" si="8"/>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="I49" s="2">
+        <f t="shared" ref="I46:I50" si="9">(E28-$Q$44)/$Q$45</f>
+        <v>-1.2998673672393632</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="C50" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D50" s="8">
-        <f>(C29-$N$44)/$N$45</f>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
       <c r="E50" s="2">
-        <f>(D40-$N$47)/$N$48</f>
-        <v>-0.44721359549995793</v>
-      </c>
-      <c r="F50" s="2">
         <f t="shared" si="2"/>
         <v>-0.44721359549995793</v>
       </c>
-      <c r="G50" s="2">
-        <f t="shared" si="3"/>
-        <v>1.4142135623730951</v>
-      </c>
-      <c r="H50" s="2">
-        <f t="shared" si="4"/>
-        <v>-0.70710678118654746</v>
-      </c>
-      <c r="I50" s="2">
-        <f t="shared" si="5"/>
-        <v>-0.70710678118654746</v>
-      </c>
-      <c r="J50" s="2">
+      <c r="F50" s="2">
         <f t="shared" si="6"/>
         <v>-0.44721359549995793</v>
       </c>
-      <c r="K50" s="2">
+      <c r="G50" s="2">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="H50" s="2">
+        <f t="shared" si="8"/>
+        <v>-0.70710678118654746</v>
+      </c>
+      <c r="I50" s="2">
+        <f>(E29-$Q$44)/$Q$45</f>
+        <v>0.92847669088525919</v>
       </c>
       <c r="M50" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N50">
         <f>AVERAGE(E35:E40)</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="P50" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q50">
-        <f>AVERAGE(J35:J40)</f>
-        <v>0.5</v>
-      </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B51" s="22">
+      <c r="B51" s="18">
         <f>AVERAGE(B45:B50)</f>
         <v>0</v>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="18">
         <f>AVERAGE(C45:C50)</f>
         <v>0</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="15">
         <f>AVERAGE(D45:D50)</f>
         <v>0</v>
       </c>
-      <c r="E51" s="19">
+      <c r="E51" s="15">
         <f>AVERAGE(E45:E50)</f>
         <v>0</v>
       </c>
-      <c r="F51" s="19">
-        <f t="shared" ref="F51:K51" si="8">AVERAGE(F45:F50)</f>
-        <v>0</v>
-      </c>
-      <c r="G51" s="19">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="19">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="19">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="19">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="19">
-        <f t="shared" si="8"/>
+      <c r="F51" s="15">
+        <f t="shared" ref="F51:K51" si="10">AVERAGE(F45:F50)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H51" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="15">
+        <f>ROUND(AVERAGE(I45:I50),10)</f>
         <v>0</v>
       </c>
       <c r="M51" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N51">
         <f>_xlfn.STDEV.P(E35:E40)</f>
         <v>0.37267799624996495</v>
       </c>
-      <c r="P51" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q51">
-        <f>_xlfn.STDEV.P(J35:J40)</f>
-        <v>0.5</v>
-      </c>
     </row>
     <row r="52" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="21">
+      <c r="B52" s="17">
         <f>_xlfn.STDEV.P(B45:B50)</f>
         <v>1</v>
       </c>
-      <c r="C52" s="21">
+      <c r="C52" s="17">
         <f>_xlfn.STDEV.P(C45:C50)</f>
         <v>1</v>
       </c>
-      <c r="D52" s="20">
+      <c r="D52" s="16">
         <f>_xlfn.STDEV.P(D45:D50)</f>
         <v>1</v>
       </c>
-      <c r="E52" s="20">
+      <c r="E52" s="16">
         <f>_xlfn.STDEV.P(E45:E50)</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="F52" s="20">
-        <f t="shared" ref="F52:K52" si="9">_xlfn.STDEV.P(F45:F50)</f>
+      <c r="F52" s="16">
+        <f t="shared" ref="F52:K52" si="11">_xlfn.STDEV.P(F45:F50)</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="G52" s="20">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="H52" s="20">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="I52" s="20">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="J52" s="20">
-        <f t="shared" si="9"/>
-        <v>1.0000000000000002</v>
-      </c>
-      <c r="K52" s="20">
-        <f t="shared" si="9"/>
+      <c r="G52" s="16">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="H52" s="16">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="I52" s="16">
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M53" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N53">
         <f>AVERAGE(F35:F40)</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="P53" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="Q53">
         <f>AVERAGE(A35:A40)</f>
@@ -2634,14 +2485,14 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M54" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="N54">
         <f>_xlfn.STDEV.P(F35:F40)</f>
         <v>0.47140452079103168</v>
       </c>
       <c r="P54" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="Q54">
         <f>_xlfn.STDEV.P(A35:A40)</f>
@@ -2650,14 +2501,14 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M56" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N56">
         <f>AVERAGE(G35:G40)</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="P56" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Q56">
         <f>AVERAGE(B35:B40)</f>
@@ -2665,16 +2516,15 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D57" s="23"/>
       <c r="M57" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N57">
         <f>_xlfn.STDEV.P(G35:G40)</f>
         <v>0.47140452079103168</v>
       </c>
       <c r="P57" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="Q57">
         <f>_xlfn.STDEV.P(B35:B40)</f>

--- a/DataIA/1.Transformaciones Variables.xlsx
+++ b/DataIA/1.Transformaciones Variables.xlsx
@@ -1939,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="2">
-        <f t="shared" ref="C35:C40" si="0">(C25-$M$40)/($M$39-$M$40)</f>
+        <f t="shared" ref="C36:C40" si="0">(C25-$M$40)/($M$39-$M$40)</f>
         <v>0.30357142857142855</v>
       </c>
       <c r="D36" s="2">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="2">
-        <f t="shared" ref="H36:H40" si="1">(E27-$M$34)/($M$33-$M$34)</f>
+        <f t="shared" ref="H38:H40" si="1">(E27-$M$34)/($M$33-$M$34)</f>
         <v>1</v>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="2">
-        <f t="shared" ref="D45:D50" si="5">(C25-$N$44)/$N$45</f>
+        <f t="shared" ref="D46:D50" si="5">(C25-$N$44)/$N$45</f>
         <v>-8.1081081081081086E-2</v>
       </c>
       <c r="E46" s="2">
@@ -2341,7 +2341,7 @@
         <v>1.4142135623730951</v>
       </c>
       <c r="I49" s="2">
-        <f t="shared" ref="I46:I50" si="9">(E28-$Q$44)/$Q$45</f>
+        <f t="shared" ref="I49" si="9">(E28-$Q$44)/$Q$45</f>
         <v>-1.2998673672393632</v>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="15">
-        <f t="shared" ref="F51:K51" si="10">AVERAGE(F45:F50)</f>
+        <f t="shared" ref="F51:H51" si="10">AVERAGE(F45:F50)</f>
         <v>0</v>
       </c>
       <c r="G51" s="15">
@@ -2451,7 +2451,7 @@
         <v>1.0000000000000002</v>
       </c>
       <c r="F52" s="16">
-        <f t="shared" ref="F52:K52" si="11">_xlfn.STDEV.P(F45:F50)</f>
+        <f t="shared" ref="F52:I52" si="11">_xlfn.STDEV.P(F45:F50)</f>
         <v>1.0000000000000002</v>
       </c>
       <c r="G52" s="16">

--- a/DataIA/1.Transformaciones Variables.xlsx
+++ b/DataIA/1.Transformaciones Variables.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D2D3B3-9FB8-4648-907F-604BCD291DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D194BE-5DDD-4CD6-A641-D2E615A02F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
